--- a/reports/weekly_report_20260615.xlsx
+++ b/reports/weekly_report_20260615.xlsx
@@ -8,9 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="核心指标" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="每日统计" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="发布明细" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="回滚明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="状态分布" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="风险级别" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="角色审批耗时" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="每日统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="发布明细" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="回滚明细" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,11 +434,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -446,7 +450,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>上周</t>
         </is>
       </c>
     </row>
@@ -457,16 +466,22 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>成功发布数</t>
+          <t>成功发布数(已发布且未回滚)</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -478,6 +493,11 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>0.00%</t>
         </is>
       </c>
@@ -491,42 +511,70 @@
       <c r="B5" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>平均审批时长(分钟)</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+          <t>失败/驳回数</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>统计开始时间</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-15T00:00:00</t>
-        </is>
-      </c>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>平均审批时长(分钟)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>统计开始时间</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T00:00:00</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>统计结束时间</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2026-06-21T23:59:59</t>
         </is>
       </c>
+      <c r="C10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -539,120 +587,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>状态</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>发布数</t>
+          <t>数量</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>回滚数</t>
+          <t>占比</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>待检查</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>前置检查失败</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>待审批</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>审批通过</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>审批驳回</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>灰度发布中</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>已发布</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>已回滚</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -666,118 +743,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>版本号</t>
+          <t>风险级别</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>风险级别</t>
+          <t>数量</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>提交人</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>稳定版本</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>是否触发回滚</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>回滚原因</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>创建时间</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>更新时间</t>
+          <t>占比</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>v2.5.0-091924</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>normal</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>precheck_failed</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>开发-小刘</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>优化巴枪扫描算法，提升分拣效率15%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>v2.4.3</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-06-19T09:19:24</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-06-19T09:19:24</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -792,18 +794,562 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>平均耗时(分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>张工(tech_lead)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>李经理(ops_lead)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>王总监(hub_manager)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>发布数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>回滚</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>版本号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>风险级别</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>提交人</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>稳定版本</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>是否加急</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>是否回滚</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>回滚原因</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>v3.0.0-apptest</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>测试员</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>审批耗时测试</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>v1.1.0-wip</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:12:59</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:13:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>v2.6.0-100438</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>前置检查失败</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>开发-小刘</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>优化分拣路径算法，加急发布</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>v2.5.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:04:38</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:04:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v1.1.0-wip</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>开发-小周</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>进行中的发布</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>v1.0.0-govtest</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:04:38</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:04:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>v1.0.0-govtest</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>开发-小陈</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>治理测试-第一次提交</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>v0.9.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:04:37</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:04:37</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -819,35 +1365,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>版本</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>影响分拨</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>异常件量</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>原因</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>回滚到版本</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>恢复版本</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>创建时间</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>完成时间</t>
         </is>

--- a/reports/weekly_report_20260615.xlsx
+++ b/reports/weekly_report_20260615.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>0</v>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
@@ -493,7 +493,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>50.00%</t>
+          <t>33.33%</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -619,11 +619,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -634,11 +634,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -664,11 +664,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -694,11 +694,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -709,11 +709,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -771,15 +771,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>emergency</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -794,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -810,42 +825,6 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>平均耗时(分钟)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>张工(tech_lead)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>李经理(ops_lead)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>王总监(hub_manager)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -980,13 +959,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1041,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1117,17 +1096,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>v3.0.0-apptest</t>
+          <t>v9.9.9-emergency-bypass</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>emergency</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>待检查</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1137,14 +1116,10 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>审批耗时测试</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>v1.1.0-wip</t>
-        </is>
-      </c>
+          <t>测试紧急发布绕过冻结窗口</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>是</t>
@@ -1158,19 +1133,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-06-19T10:12:59</t>
+          <t>2026-06-19T10:45:56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-06-19T10:13:01</t>
+          <t>2026-06-19T10:45:56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>v2.6.0-100438</t>
+          <t>v4.0.0-stable</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1180,27 +1155,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>前置检查失败</t>
+          <t>已发布</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>开发-小刘</t>
+          <t>测试员</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>优化分拣路径算法，加急发布</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>v2.5.0</t>
-        </is>
-      </c>
+          <t>基线稳定版本</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1211,19 +1182,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-06-19T10:04:38</t>
+          <t>2026-06-19T10:45:56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-06-19T10:04:38</t>
+          <t>2026-06-19T10:45:56</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1.1.0-wip</t>
+          <t>v5.0.0-A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1233,24 +1204,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>已发布</t>
+          <t>灰度发布中</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>开发-小周</t>
+          <t>测试员</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>进行中的发布</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>v1.0.0-govtest</t>
-        </is>
-      </c>
+          <t>test v5.0.0-A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>否</t>
@@ -1264,65 +1231,12 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-06-19T10:04:38</t>
+          <t>2026-06-19T10:45:56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-06-19T10:04:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>v1.0.0-govtest</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>已发布</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>开发-小陈</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>治理测试-第一次提交</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>v0.9.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-19T10:04:37</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-06-19T10:04:37</t>
+          <t>2026-06-19T10:45:56</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report_20260615.xlsx
+++ b/reports/weekly_report_20260615.xlsx
@@ -1096,7 +1096,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>v9.9.9-emergency-bypass</t>
+          <t>v9.9.9-demo-emergency</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>测试员</t>
+          <t>紧急值班</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>测试紧急发布绕过冻结窗口</t>
+          <t>演示紧急发布绕过冻结窗口</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -1133,19 +1133,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-06-19T10:45:56</t>
+          <t>2026-06-19T11:04:19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-06-19T10:45:56</t>
+          <t>2026-06-19T11:04:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>v4.0.0-stable</t>
+          <t>v6.1.0-dc01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>已发布</t>
+          <t>灰度发布中</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>测试员</t>
+          <t>开发A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>基线稳定版本</t>
+          <t>华北地区专属</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -1182,19 +1182,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-06-19T10:45:56</t>
+          <t>2026-06-19T11:04:19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-06-19T10:45:56</t>
+          <t>2026-06-19T11:04:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v5.0.0-A</t>
+          <t>v6.0.0-stable</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>灰度发布中</t>
+          <t>已发布</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>测试员</t>
+          <t>发布管理员</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>test v5.0.0-A</t>
+          <t>稳定基线</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -1231,12 +1231,12 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-06-19T10:45:56</t>
+          <t>2026-06-19T11:04:19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-06-19T10:45:56</t>
+          <t>2026-06-19T11:04:19</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report_20260615.xlsx
+++ b/reports/weekly_report_20260615.xlsx
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
@@ -493,7 +493,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>33.33%</t>
+          <t>66.67%</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
     </row>
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -619,11 +619,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -705,28 +705,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>已发布</t>
+          <t>已暂停</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>已回滚</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -743,7 +758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -775,26 +790,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>v9.9.9-demo-emergency</t>
+          <t>v7.2.0-pausetest</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1106,23 +1106,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>待检查</t>
+          <t>灰度发布中</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>紧急值班</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>演示紧急发布绕过冻结窗口</t>
+          <t>暂停恢复测试版本</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1133,45 +1133,45 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-06-19T11:04:19</t>
+          <t>2026-06-19T12:10:09</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-06-19T11:04:19</t>
+          <t>2026-06-19T12:10:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>v6.1.0-dc01</t>
+          <t>v7.1.0-small</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>emergency</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>灰度发布中</t>
+          <t>已发布</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>开发A</t>
+          <t>测试开发</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>华北地区专属</t>
+          <t>定向DC009 DC010小版本</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1182,24 +1182,24 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-06-19T11:04:19</t>
+          <t>2026-06-19T12:10:09</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-06-19T11:04:19</t>
+          <t>2026-06-19T12:10:09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v6.0.0-stable</t>
+          <t>v7.0.0-stable</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>emergency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>发布管理员</t>
+          <t>管理员</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>稳定基线</t>
+          <t>基线版本</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -1231,12 +1231,12 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-06-19T11:04:19</t>
+          <t>2026-06-19T12:10:09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-06-19T11:04:19</t>
+          <t>2026-06-19T12:10:09</t>
         </is>
       </c>
     </row>
